--- a/data/ams_weekly_data/White_Mulberry/ads_report_week10.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\ams_weekly_data\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACAC5EA-1EC0-4BC2-B14B-E7FC8CD3AEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37899FB6-481D-4BA5-BF88-2795C4B22F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{C2EB3544-0B30-4B5A-9817-98DE85FBF6BC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C2EB3544-0B30-4B5A-9817-98DE85FBF6BC}"/>
   </bookViews>
   <sheets>
     <sheet name="SP" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4023" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4139" uniqueCount="116">
   <si>
     <t>Brand</t>
   </si>
@@ -376,6 +376,21 @@
   </si>
   <si>
     <t>B0DQ4YWSMC</t>
+  </si>
+  <si>
+    <t>SBV_KT_Gas Spring Monitor Arm_WM-GS1M-BK</t>
+  </si>
+  <si>
+    <t>SBV_KT_Wooden Finish Monitor Arm_HDWF1ML</t>
+  </si>
+  <si>
+    <t>SBV_KT_Wall Mount Monitor Arm_WM1ML</t>
+  </si>
+  <si>
+    <t>SBV_B0CPFS24ML_Keyword_BMC</t>
+  </si>
+  <si>
+    <t>SB_Sit Stand Desk_KT_Reach_BMC</t>
   </si>
 </sst>
 </file>
@@ -735,10 +750,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EF6D63-3663-4E20-A7FC-263D078FDDB8}">
-  <dimension ref="A1:I928"/>
+  <dimension ref="A1:I957"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -27650,6 +27666,847 @@
         <v>0</v>
       </c>
       <c r="I928" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="929" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A929" t="s">
+        <v>9</v>
+      </c>
+      <c r="B929" t="s">
+        <v>111</v>
+      </c>
+      <c r="C929" t="s">
+        <v>35</v>
+      </c>
+      <c r="D929">
+        <v>3998</v>
+      </c>
+      <c r="E929">
+        <v>44</v>
+      </c>
+      <c r="F929">
+        <v>336.1</v>
+      </c>
+      <c r="G929">
+        <v>0</v>
+      </c>
+      <c r="H929">
+        <v>0</v>
+      </c>
+      <c r="I929" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="930" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A930" t="s">
+        <v>9</v>
+      </c>
+      <c r="B930" t="s">
+        <v>111</v>
+      </c>
+      <c r="C930" t="s">
+        <v>35</v>
+      </c>
+      <c r="D930">
+        <v>4174</v>
+      </c>
+      <c r="E930">
+        <v>37</v>
+      </c>
+      <c r="F930">
+        <v>304.06</v>
+      </c>
+      <c r="G930">
+        <v>2287.29</v>
+      </c>
+      <c r="H930">
+        <v>1</v>
+      </c>
+      <c r="I930" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="931" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A931" t="s">
+        <v>9</v>
+      </c>
+      <c r="B931" t="s">
+        <v>111</v>
+      </c>
+      <c r="C931" t="s">
+        <v>35</v>
+      </c>
+      <c r="D931">
+        <v>5701</v>
+      </c>
+      <c r="E931">
+        <v>42</v>
+      </c>
+      <c r="F931">
+        <v>391.21</v>
+      </c>
+      <c r="G931">
+        <v>2287.29</v>
+      </c>
+      <c r="H931">
+        <v>1</v>
+      </c>
+      <c r="I931" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="932" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A932" t="s">
+        <v>9</v>
+      </c>
+      <c r="B932" t="s">
+        <v>111</v>
+      </c>
+      <c r="C932" t="s">
+        <v>35</v>
+      </c>
+      <c r="D932">
+        <v>3887</v>
+      </c>
+      <c r="E932">
+        <v>40</v>
+      </c>
+      <c r="F932">
+        <v>414.62</v>
+      </c>
+      <c r="G932">
+        <v>2287.2800000000002</v>
+      </c>
+      <c r="H932">
+        <v>1</v>
+      </c>
+      <c r="I932" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="933" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A933" t="s">
+        <v>9</v>
+      </c>
+      <c r="B933" t="s">
+        <v>111</v>
+      </c>
+      <c r="C933" t="s">
+        <v>35</v>
+      </c>
+      <c r="D933">
+        <v>7240</v>
+      </c>
+      <c r="E933">
+        <v>39</v>
+      </c>
+      <c r="F933">
+        <v>367.82</v>
+      </c>
+      <c r="G933">
+        <v>2287.29</v>
+      </c>
+      <c r="H933">
+        <v>1</v>
+      </c>
+      <c r="I933" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="934" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A934" t="s">
+        <v>9</v>
+      </c>
+      <c r="B934" t="s">
+        <v>111</v>
+      </c>
+      <c r="C934" t="s">
+        <v>35</v>
+      </c>
+      <c r="D934">
+        <v>8517</v>
+      </c>
+      <c r="E934">
+        <v>54</v>
+      </c>
+      <c r="F934">
+        <v>504.08</v>
+      </c>
+      <c r="G934">
+        <v>11182.21</v>
+      </c>
+      <c r="H934">
+        <v>5</v>
+      </c>
+      <c r="I934" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="935" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A935" t="s">
+        <v>9</v>
+      </c>
+      <c r="B935" t="s">
+        <v>111</v>
+      </c>
+      <c r="C935" t="s">
+        <v>35</v>
+      </c>
+      <c r="D935">
+        <v>4941</v>
+      </c>
+      <c r="E935">
+        <v>63</v>
+      </c>
+      <c r="F935">
+        <v>684.16</v>
+      </c>
+      <c r="G935">
+        <v>2626.27</v>
+      </c>
+      <c r="H935">
+        <v>1</v>
+      </c>
+      <c r="I935" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="936" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A936" t="s">
+        <v>9</v>
+      </c>
+      <c r="B936" t="s">
+        <v>112</v>
+      </c>
+      <c r="C936" t="s">
+        <v>36</v>
+      </c>
+      <c r="D936">
+        <v>0</v>
+      </c>
+      <c r="E936">
+        <v>0</v>
+      </c>
+      <c r="F936">
+        <v>0</v>
+      </c>
+      <c r="G936">
+        <v>0</v>
+      </c>
+      <c r="H936">
+        <v>0</v>
+      </c>
+      <c r="I936" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="937" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A937" t="s">
+        <v>9</v>
+      </c>
+      <c r="B937" t="s">
+        <v>112</v>
+      </c>
+      <c r="C937" t="s">
+        <v>36</v>
+      </c>
+      <c r="D937">
+        <v>0</v>
+      </c>
+      <c r="E937">
+        <v>0</v>
+      </c>
+      <c r="F937">
+        <v>0</v>
+      </c>
+      <c r="G937">
+        <v>0</v>
+      </c>
+      <c r="H937">
+        <v>0</v>
+      </c>
+      <c r="I937" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="938" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A938" t="s">
+        <v>9</v>
+      </c>
+      <c r="B938" t="s">
+        <v>112</v>
+      </c>
+      <c r="C938" t="s">
+        <v>36</v>
+      </c>
+      <c r="D938">
+        <v>0</v>
+      </c>
+      <c r="E938">
+        <v>0</v>
+      </c>
+      <c r="F938">
+        <v>0</v>
+      </c>
+      <c r="G938">
+        <v>0</v>
+      </c>
+      <c r="H938">
+        <v>0</v>
+      </c>
+      <c r="I938" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="939" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A939" t="s">
+        <v>9</v>
+      </c>
+      <c r="B939" t="s">
+        <v>112</v>
+      </c>
+      <c r="C939" t="s">
+        <v>36</v>
+      </c>
+      <c r="D939">
+        <v>0</v>
+      </c>
+      <c r="E939">
+        <v>0</v>
+      </c>
+      <c r="F939">
+        <v>0</v>
+      </c>
+      <c r="G939">
+        <v>0</v>
+      </c>
+      <c r="H939">
+        <v>0</v>
+      </c>
+      <c r="I939" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="940" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A940" t="s">
+        <v>9</v>
+      </c>
+      <c r="B940" t="s">
+        <v>112</v>
+      </c>
+      <c r="C940" t="s">
+        <v>36</v>
+      </c>
+      <c r="D940">
+        <v>0</v>
+      </c>
+      <c r="E940">
+        <v>0</v>
+      </c>
+      <c r="F940">
+        <v>0</v>
+      </c>
+      <c r="G940">
+        <v>0</v>
+      </c>
+      <c r="H940">
+        <v>0</v>
+      </c>
+      <c r="I940" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="941" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A941" t="s">
+        <v>9</v>
+      </c>
+      <c r="B941" t="s">
+        <v>112</v>
+      </c>
+      <c r="C941" t="s">
+        <v>36</v>
+      </c>
+      <c r="D941">
+        <v>0</v>
+      </c>
+      <c r="E941">
+        <v>0</v>
+      </c>
+      <c r="F941">
+        <v>0</v>
+      </c>
+      <c r="G941">
+        <v>0</v>
+      </c>
+      <c r="H941">
+        <v>0</v>
+      </c>
+      <c r="I941" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="942" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A942" t="s">
+        <v>9</v>
+      </c>
+      <c r="B942" t="s">
+        <v>112</v>
+      </c>
+      <c r="C942" t="s">
+        <v>36</v>
+      </c>
+      <c r="D942">
+        <v>0</v>
+      </c>
+      <c r="E942">
+        <v>0</v>
+      </c>
+      <c r="F942">
+        <v>0</v>
+      </c>
+      <c r="G942">
+        <v>0</v>
+      </c>
+      <c r="H942">
+        <v>0</v>
+      </c>
+      <c r="I942" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="943" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A943" t="s">
+        <v>9</v>
+      </c>
+      <c r="B943" t="s">
+        <v>113</v>
+      </c>
+      <c r="C943" t="s">
+        <v>38</v>
+      </c>
+      <c r="D943">
+        <v>0</v>
+      </c>
+      <c r="E943">
+        <v>0</v>
+      </c>
+      <c r="F943">
+        <v>0</v>
+      </c>
+      <c r="G943">
+        <v>0</v>
+      </c>
+      <c r="H943">
+        <v>0</v>
+      </c>
+      <c r="I943" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="944" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A944" t="s">
+        <v>9</v>
+      </c>
+      <c r="B944" t="s">
+        <v>113</v>
+      </c>
+      <c r="C944" t="s">
+        <v>38</v>
+      </c>
+      <c r="D944">
+        <v>0</v>
+      </c>
+      <c r="E944">
+        <v>0</v>
+      </c>
+      <c r="F944">
+        <v>0</v>
+      </c>
+      <c r="G944">
+        <v>0</v>
+      </c>
+      <c r="H944">
+        <v>0</v>
+      </c>
+      <c r="I944" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="945" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A945" t="s">
+        <v>9</v>
+      </c>
+      <c r="B945" t="s">
+        <v>113</v>
+      </c>
+      <c r="C945" t="s">
+        <v>38</v>
+      </c>
+      <c r="D945">
+        <v>0</v>
+      </c>
+      <c r="E945">
+        <v>0</v>
+      </c>
+      <c r="F945">
+        <v>0</v>
+      </c>
+      <c r="G945">
+        <v>0</v>
+      </c>
+      <c r="H945">
+        <v>0</v>
+      </c>
+      <c r="I945" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="946" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A946" t="s">
+        <v>9</v>
+      </c>
+      <c r="B946" t="s">
+        <v>113</v>
+      </c>
+      <c r="C946" t="s">
+        <v>38</v>
+      </c>
+      <c r="D946">
+        <v>0</v>
+      </c>
+      <c r="E946">
+        <v>0</v>
+      </c>
+      <c r="F946">
+        <v>0</v>
+      </c>
+      <c r="G946">
+        <v>0</v>
+      </c>
+      <c r="H946">
+        <v>0</v>
+      </c>
+      <c r="I946" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="947" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A947" t="s">
+        <v>9</v>
+      </c>
+      <c r="B947" t="s">
+        <v>113</v>
+      </c>
+      <c r="C947" t="s">
+        <v>38</v>
+      </c>
+      <c r="D947">
+        <v>0</v>
+      </c>
+      <c r="E947">
+        <v>0</v>
+      </c>
+      <c r="F947">
+        <v>0</v>
+      </c>
+      <c r="G947">
+        <v>0</v>
+      </c>
+      <c r="H947">
+        <v>0</v>
+      </c>
+      <c r="I947" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="948" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A948" t="s">
+        <v>9</v>
+      </c>
+      <c r="B948" t="s">
+        <v>113</v>
+      </c>
+      <c r="C948" t="s">
+        <v>38</v>
+      </c>
+      <c r="D948">
+        <v>0</v>
+      </c>
+      <c r="E948">
+        <v>0</v>
+      </c>
+      <c r="F948">
+        <v>0</v>
+      </c>
+      <c r="G948">
+        <v>0</v>
+      </c>
+      <c r="H948">
+        <v>0</v>
+      </c>
+      <c r="I948" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="949" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A949" t="s">
+        <v>9</v>
+      </c>
+      <c r="B949" t="s">
+        <v>113</v>
+      </c>
+      <c r="C949" t="s">
+        <v>38</v>
+      </c>
+      <c r="D949">
+        <v>77</v>
+      </c>
+      <c r="E949">
+        <v>6</v>
+      </c>
+      <c r="F949">
+        <v>31.57</v>
+      </c>
+      <c r="G949">
+        <v>0</v>
+      </c>
+      <c r="H949">
+        <v>0</v>
+      </c>
+      <c r="I949" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="950" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A950" t="s">
+        <v>50</v>
+      </c>
+      <c r="B950" t="s">
+        <v>114</v>
+      </c>
+      <c r="C950" t="s">
+        <v>55</v>
+      </c>
+      <c r="D950">
+        <v>21801</v>
+      </c>
+      <c r="E950" s="1">
+        <v>122</v>
+      </c>
+      <c r="F950">
+        <v>1396.67</v>
+      </c>
+      <c r="G950">
+        <v>0</v>
+      </c>
+      <c r="H950">
+        <v>0</v>
+      </c>
+      <c r="I950" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="951" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A951" t="s">
+        <v>50</v>
+      </c>
+      <c r="B951" t="s">
+        <v>114</v>
+      </c>
+      <c r="C951" t="s">
+        <v>55</v>
+      </c>
+      <c r="D951">
+        <v>43478</v>
+      </c>
+      <c r="E951" s="1">
+        <v>207</v>
+      </c>
+      <c r="F951">
+        <v>2324.23</v>
+      </c>
+      <c r="G951">
+        <v>0</v>
+      </c>
+      <c r="H951">
+        <v>0</v>
+      </c>
+      <c r="I951" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="952" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A952" t="s">
+        <v>50</v>
+      </c>
+      <c r="B952" t="s">
+        <v>114</v>
+      </c>
+      <c r="C952" t="s">
+        <v>55</v>
+      </c>
+      <c r="D952">
+        <v>14216</v>
+      </c>
+      <c r="E952" s="1">
+        <v>73</v>
+      </c>
+      <c r="F952">
+        <v>789.94</v>
+      </c>
+      <c r="G952">
+        <v>0</v>
+      </c>
+      <c r="H952">
+        <v>0</v>
+      </c>
+      <c r="I952" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="953" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A953" t="s">
+        <v>50</v>
+      </c>
+      <c r="B953" t="s">
+        <v>114</v>
+      </c>
+      <c r="C953" t="s">
+        <v>55</v>
+      </c>
+      <c r="D953">
+        <v>37843</v>
+      </c>
+      <c r="E953" s="1">
+        <v>208</v>
+      </c>
+      <c r="F953">
+        <v>1854.63</v>
+      </c>
+      <c r="G953">
+        <v>0</v>
+      </c>
+      <c r="H953">
+        <v>0</v>
+      </c>
+      <c r="I953" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="954" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A954" t="s">
+        <v>50</v>
+      </c>
+      <c r="B954" t="s">
+        <v>114</v>
+      </c>
+      <c r="C954" t="s">
+        <v>55</v>
+      </c>
+      <c r="D954">
+        <v>3110</v>
+      </c>
+      <c r="E954" s="1">
+        <v>19</v>
+      </c>
+      <c r="F954">
+        <v>190.98</v>
+      </c>
+      <c r="G954">
+        <v>0</v>
+      </c>
+      <c r="H954">
+        <v>0</v>
+      </c>
+      <c r="I954" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="955" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A955" t="s">
+        <v>60</v>
+      </c>
+      <c r="B955" t="s">
+        <v>115</v>
+      </c>
+      <c r="C955" t="s">
+        <v>99</v>
+      </c>
+      <c r="D955">
+        <v>966</v>
+      </c>
+      <c r="E955">
+        <v>20</v>
+      </c>
+      <c r="F955">
+        <v>333</v>
+      </c>
+      <c r="G955">
+        <v>2287.8533333333335</v>
+      </c>
+      <c r="H955">
+        <v>1</v>
+      </c>
+      <c r="I955" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="956" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A956" t="s">
+        <v>60</v>
+      </c>
+      <c r="B956" t="s">
+        <v>115</v>
+      </c>
+      <c r="C956" t="s">
+        <v>110</v>
+      </c>
+      <c r="D956">
+        <v>966</v>
+      </c>
+      <c r="E956">
+        <v>20</v>
+      </c>
+      <c r="F956">
+        <v>333</v>
+      </c>
+      <c r="G956">
+        <v>2287.8533333333335</v>
+      </c>
+      <c r="H956">
+        <v>0</v>
+      </c>
+      <c r="I956" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="957" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A957" t="s">
+        <v>60</v>
+      </c>
+      <c r="B957" t="s">
+        <v>115</v>
+      </c>
+      <c r="C957" t="s">
+        <v>109</v>
+      </c>
+      <c r="D957">
+        <v>966</v>
+      </c>
+      <c r="E957">
+        <v>20</v>
+      </c>
+      <c r="F957">
+        <v>333</v>
+      </c>
+      <c r="G957">
+        <v>2287.8533333333335</v>
+      </c>
+      <c r="H957">
+        <v>0</v>
+      </c>
+      <c r="I957" t="s">
         <v>49</v>
       </c>
     </row>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week10.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week10.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4841,4 +4842,60 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>